--- a/Collections/Ukraine/#Ukraine#Regular#[1992-present]#circulation_quality.xlsx
+++ b/Collections/Ukraine/#Ukraine#Regular#[1992-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Ukraine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C34E03-5404-4020-80A3-524497BE7F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD04F03-D1CC-479C-B536-6EBAA4FD7557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1копійка" sheetId="4" r:id="rId1"/>
@@ -1602,71 +1602,7 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="251">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="248">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
@@ -1675,6 +1611,46 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -3617,9 +3593,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="9" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4455,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4988,12 +4964,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:G27 H24:H27 G29:H29">
-    <cfRule type="containsText" dxfId="250" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="247" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="249" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="246" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5010,11 +4986,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H10">
-    <cfRule type="containsText" dxfId="248" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="245" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23 H21">
+  <conditionalFormatting sqref="H21 H23">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5027,7 +5003,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21 H23">
-    <cfRule type="containsText" dxfId="247" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="244" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5044,7 +5020,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:H20 H22">
-    <cfRule type="containsText" dxfId="246" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="243" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5061,7 +5037,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="245" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="242" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5078,7 +5054,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="244" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="241" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5095,7 +5071,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32:G33">
-    <cfRule type="containsText" dxfId="243" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="240" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5112,7 +5088,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G30:G31">
-    <cfRule type="containsText" dxfId="242" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="239" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5129,7 +5105,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="241" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="238" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5146,7 +5122,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="240" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="237" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5163,7 +5139,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30:H31">
-    <cfRule type="containsText" dxfId="239" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="236" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5180,7 +5156,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:H33">
-    <cfRule type="containsText" dxfId="238" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="235" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5197,7 +5173,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34:G36">
-    <cfRule type="containsText" dxfId="237" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="234" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5214,7 +5190,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:H36">
-    <cfRule type="containsText" dxfId="236" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="233" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5243,7 +5219,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="235" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="232" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5260,7 +5236,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="234" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="231" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5277,7 +5253,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="233" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="230" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5294,12 +5270,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="232" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="229" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="231" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="228" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5316,7 +5292,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="230" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="227" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5333,7 +5309,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="229" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="226" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5414,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="19" t="str">
-        <f t="shared" ref="G3:G35" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G3:G34" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
       <c r="H3" s="18"/>
@@ -6223,11 +6199,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F28">
-    <cfRule type="containsText" dxfId="16" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34 F32 F36">
+  <conditionalFormatting sqref="F32 F34 F36">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6240,7 +6216,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32 F34 F36">
-    <cfRule type="containsText" dxfId="15" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6257,7 +6233,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F30">
-    <cfRule type="containsText" dxfId="14" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6274,7 +6250,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6291,7 +6267,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6308,7 +6284,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7433,7 +7409,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23 H21">
+  <conditionalFormatting sqref="H21 H23">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7446,12 +7422,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:H13 H22 H15:H20">
-    <cfRule type="containsText" dxfId="228" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="225" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21 H23">
-    <cfRule type="containsText" dxfId="227" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="224" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7516,32 +7492,32 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:G27 H24:H27 G29:H29">
-    <cfRule type="containsText" dxfId="226" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="223" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:H10">
-    <cfRule type="containsText" dxfId="225" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="222" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="224" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="221" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="223" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="220" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="222" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="219" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="221" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="218" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7558,7 +7534,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="220" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="217" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7575,7 +7551,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="219" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="216" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7592,7 +7568,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="218" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="215" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7609,7 +7585,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="217" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="214" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7626,7 +7602,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="216" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="213" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7643,7 +7619,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="215" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="212" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7660,7 +7636,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G30:G31">
-    <cfRule type="containsText" dxfId="214" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="211" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7677,7 +7653,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30:H31">
-    <cfRule type="containsText" dxfId="213" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="210" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7694,7 +7670,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32:G33">
-    <cfRule type="containsText" dxfId="212" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="209" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7711,7 +7687,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:H33">
-    <cfRule type="containsText" dxfId="211" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="208" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7728,7 +7704,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34:G36">
-    <cfRule type="containsText" dxfId="210" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="207" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7745,7 +7721,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:H36">
-    <cfRule type="containsText" dxfId="209" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="206" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7762,7 +7738,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="208" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="205" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7779,7 +7755,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="207" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="204" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7796,7 +7772,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="206" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="203" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8900,7 +8876,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23 H21 H25">
+  <conditionalFormatting sqref="H21 H23 H25">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8913,22 +8889,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H20 H22 H24 H26">
-    <cfRule type="containsText" dxfId="205" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="202" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21 H23 H25">
-    <cfRule type="containsText" dxfId="204" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="201" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:G12 G14:G27 G29">
-    <cfRule type="containsText" dxfId="203" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="200" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="202" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="199" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8981,27 +8957,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="201" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="198" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:H10">
-    <cfRule type="containsText" dxfId="200" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="197" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="199" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="196" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="198" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="195" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="197" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="194" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9018,7 +8994,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="196" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="193" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9035,7 +9011,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="195" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="192" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9052,7 +9028,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="194" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="191" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9069,7 +9045,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="193" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="190" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9086,7 +9062,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="192" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="189" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9103,7 +9079,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G30:G31">
-    <cfRule type="containsText" dxfId="191" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="188" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9120,7 +9096,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30:H31">
-    <cfRule type="containsText" dxfId="190" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="187" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9137,7 +9113,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32:G33">
-    <cfRule type="containsText" dxfId="189" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="186" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9154,7 +9130,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:H33">
-    <cfRule type="containsText" dxfId="188" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="185" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9171,7 +9147,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34:G36">
-    <cfRule type="containsText" dxfId="187" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="184" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9188,7 +9164,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:H36">
-    <cfRule type="containsText" dxfId="186" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="183" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9205,7 +9181,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="185" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="182" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9222,7 +9198,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="containsText" dxfId="184" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="181" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9239,7 +9215,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="183" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="180" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9256,7 +9232,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="182" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="179" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9273,7 +9249,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="181" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="178" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9290,7 +9266,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="180" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="177" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9307,7 +9283,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="179" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="176" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9936,7 +9912,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="12" t="str">
         <f t="shared" si="0"/>
@@ -10343,7 +10319,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24 H22 H26 H28 H34">
+  <conditionalFormatting sqref="H22 H24 H26 H28 H34">
     <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10368,12 +10344,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H21 H23 H25 H27 H31">
-    <cfRule type="containsText" dxfId="178" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="175" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22 H24 H26 H28 H34">
-    <cfRule type="containsText" dxfId="177" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="174" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10426,27 +10402,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G12 G14:G28 G31:G34 H4">
-    <cfRule type="containsText" dxfId="176" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="173" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H11">
-    <cfRule type="containsText" dxfId="175" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="172" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="174" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="171" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="173" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="170" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="172" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="169" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10463,7 +10439,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="171" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="168" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10504,22 +10480,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="170" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="167" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="169" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="166" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="168" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="165" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="167" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="164" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10536,7 +10512,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="166" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="163" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10553,7 +10529,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="containsText" dxfId="165" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="162" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10570,7 +10546,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:H33">
-    <cfRule type="containsText" dxfId="164" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="161" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10587,7 +10563,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G37">
-    <cfRule type="containsText" dxfId="163" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="160" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10604,7 +10580,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:H37">
-    <cfRule type="containsText" dxfId="162" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="159" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10621,7 +10597,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G30">
-    <cfRule type="containsText" dxfId="161" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="158" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10638,7 +10614,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30">
-    <cfRule type="containsText" dxfId="160" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="157" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10655,7 +10631,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29">
-    <cfRule type="containsText" dxfId="159" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="156" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10672,7 +10648,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="158" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="155" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10689,17 +10665,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="157" priority="6" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="154" priority="6" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="156" priority="4" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="153" priority="4" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="155" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="152" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10716,7 +10692,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="154" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="151" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11991,7 +11967,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J25 J23 J27 J18:J21">
+  <conditionalFormatting sqref="J23 J25 J27 J18:J21">
     <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -12039,7 +12015,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J24 J22 J26">
+  <conditionalFormatting sqref="J22 J24 J26">
     <cfRule type="colorScale" priority="110">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -12052,17 +12028,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23 J25 J27 J18:J21">
-    <cfRule type="containsText" dxfId="153" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="150" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J22 J24 J26">
-    <cfRule type="containsText" dxfId="152" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="149" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H11 H14:H16 H30 H18:H28">
-    <cfRule type="containsText" dxfId="151" priority="119" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="148" priority="119" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12127,12 +12103,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11 I14:I16 I30 I18:I28">
-    <cfRule type="containsText" dxfId="150" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="147" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8:J11">
-    <cfRule type="containsText" dxfId="149" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="146" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12149,12 +12125,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H9">
-    <cfRule type="containsText" dxfId="148" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="145" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="containsText" dxfId="147" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="144" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12171,22 +12147,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5">
-    <cfRule type="containsText" dxfId="146" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="143" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="145" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="142" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3">
-    <cfRule type="containsText" dxfId="144" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="141" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6">
-    <cfRule type="containsText" dxfId="143" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="140" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12203,7 +12179,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="containsText" dxfId="142" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="139" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12220,7 +12196,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="141" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="138" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12249,12 +12225,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="140" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="137" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="139" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="136" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12283,12 +12259,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6">
-    <cfRule type="containsText" dxfId="138" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="135" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="137" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="134" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12305,12 +12281,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="136" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="133" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J14))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="135" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="132" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12327,7 +12303,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="134" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="131" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12344,17 +12320,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J35:J37">
-    <cfRule type="containsText" dxfId="133" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="130" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J35))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I35:I37">
-    <cfRule type="containsText" dxfId="132" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="129" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I35))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J29">
-    <cfRule type="containsText" dxfId="131" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="128" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12371,12 +12347,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31:H32">
-    <cfRule type="containsText" dxfId="130" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="127" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31:I32">
-    <cfRule type="containsText" dxfId="129" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="126" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12393,7 +12369,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33:H34">
-    <cfRule type="containsText" dxfId="128" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="125" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12410,7 +12386,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I33:I34">
-    <cfRule type="containsText" dxfId="127" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="124" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12427,7 +12403,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:H37">
-    <cfRule type="containsText" dxfId="126" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="123" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12456,7 +12432,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:J32">
-    <cfRule type="containsText" dxfId="125" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="122" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12473,7 +12449,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J33:J34">
-    <cfRule type="containsText" dxfId="124" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="121" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12490,7 +12466,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="123" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="120" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12507,7 +12483,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29">
-    <cfRule type="containsText" dxfId="122" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="119" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12548,12 +12524,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4">
-    <cfRule type="containsText" dxfId="121" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="118" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="120" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="117" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12570,7 +12546,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="119" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="116" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12587,7 +12563,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="118" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="115" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12604,7 +12580,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="117" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="114" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12633,7 +12609,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="containsText" dxfId="116" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="113" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12650,7 +12626,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17">
-    <cfRule type="containsText" dxfId="115" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="112" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I17))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12667,12 +12643,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17">
-    <cfRule type="containsText" dxfId="114" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="111" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J17))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16">
-    <cfRule type="containsText" dxfId="113" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="110" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J16))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12689,7 +12665,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="112" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="109" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J15))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12706,7 +12682,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="111" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="108" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12723,7 +12699,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J30">
-    <cfRule type="containsText" dxfId="110" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="107" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12740,7 +12716,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J28">
-    <cfRule type="containsText" dxfId="109" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="106" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13920,7 +13896,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H28 H22">
+  <conditionalFormatting sqref="H22 H28">
     <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13933,12 +13909,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:H21">
-    <cfRule type="containsText" dxfId="108" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="105" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22 H28">
-    <cfRule type="containsText" dxfId="107" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="104" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13979,12 +13955,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G11 G14:G24 G32:G33 G28 G30">
-    <cfRule type="containsText" dxfId="106" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="103" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H11">
-    <cfRule type="containsText" dxfId="105" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="102" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14001,22 +13977,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="104" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="101" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="103" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="100" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="102" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="99" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="101" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="98" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14033,7 +14009,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="100" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="97" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14062,12 +14038,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G12">
-    <cfRule type="containsText" dxfId="99" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="96" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="98" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="95" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14084,7 +14060,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="97" priority="139" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="94" priority="139" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14113,7 +14089,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="96" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="93" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14130,7 +14106,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="containsText" dxfId="95" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="92" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14147,7 +14123,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="94" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="91" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14164,7 +14140,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="93" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="90" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14181,7 +14157,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="containsText" dxfId="92" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="89" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14198,7 +14174,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="91" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="88" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14227,17 +14203,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="containsText" dxfId="90" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="87" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G31">
-    <cfRule type="containsText" dxfId="89" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="86" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G31))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="containsText" dxfId="88" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="85" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14254,12 +14230,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="containsText" dxfId="87" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="84" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="86" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="83" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14276,7 +14252,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="85" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="82" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14293,7 +14269,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="84" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="81" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14322,7 +14298,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15">
-    <cfRule type="containsText" dxfId="83" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="80" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14339,7 +14315,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="containsText" dxfId="82" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="79" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14356,7 +14332,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="containsText" dxfId="81" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="78" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14373,7 +14349,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23:H24">
-    <cfRule type="containsText" dxfId="80" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="77" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14390,7 +14366,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="79" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="76" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14407,7 +14383,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30">
-    <cfRule type="containsText" dxfId="78" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="75" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14424,7 +14400,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="77" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="74" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14441,7 +14417,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26">
-    <cfRule type="containsText" dxfId="76" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="73" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14458,7 +14434,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25">
-    <cfRule type="containsText" dxfId="75" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="72" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14475,7 +14451,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="containsText" dxfId="74" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="71" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14504,7 +14480,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29">
-    <cfRule type="containsText" dxfId="73" priority="32" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="70" priority="32" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14521,7 +14497,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="72" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="69" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14538,7 +14514,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="containsText" dxfId="71" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="68" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14555,7 +14531,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34">
-    <cfRule type="containsText" dxfId="70" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="67" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14572,7 +14548,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35">
-    <cfRule type="containsText" dxfId="69" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="66" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14589,7 +14565,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36">
-    <cfRule type="containsText" dxfId="68" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14606,7 +14582,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35">
-    <cfRule type="containsText" dxfId="67" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="64" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14623,7 +14599,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H36">
-    <cfRule type="containsText" dxfId="66" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="63" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14640,7 +14616,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G37">
-    <cfRule type="containsText" dxfId="65" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="62" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G37))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14657,7 +14633,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37">
-    <cfRule type="containsText" dxfId="64" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="61" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14674,7 +14650,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G39">
-    <cfRule type="containsText" dxfId="63" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G39))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14691,12 +14667,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="containsText" dxfId="62" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="59" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="containsText" dxfId="61" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="58" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14713,7 +14689,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38">
-    <cfRule type="containsText" dxfId="60" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="57" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G38))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14730,7 +14706,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="56" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14747,7 +14723,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40">
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="55" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G40))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15849,7 +15825,7 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H27 H22 H13:H17 H33 H35 H37">
+  <conditionalFormatting sqref="H22 H27 H13:H17 H33 H35 H37">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -15909,7 +15885,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23 H21 H26 H28 H30">
+  <conditionalFormatting sqref="H21 H23 H26 H28 H30">
     <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -15922,17 +15898,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22 H27 H13:H17 H33 H35 H37">
-    <cfRule type="containsText" dxfId="59" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="54" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21 H23 H26 H28 H30">
-    <cfRule type="containsText" dxfId="58" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="53" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="57" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="52" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15961,17 +15937,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="56" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="51" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:G10 G14:G17 G30 G21:G24 G19 G26:G28 G33 G35 G37">
-    <cfRule type="containsText" dxfId="55" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="50" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:H10">
-    <cfRule type="containsText" dxfId="54" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="49" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15988,17 +15964,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G5">
-    <cfRule type="containsText" dxfId="53" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="48" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H5">
-    <cfRule type="containsText" dxfId="52" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="47" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="containsText" dxfId="51" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="46" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16015,7 +15991,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="50" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16044,12 +16020,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="49" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="44" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="48" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16078,12 +16054,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="47" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G18">
-    <cfRule type="containsText" dxfId="46" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="41" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G18))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16124,12 +16100,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29">
-    <cfRule type="containsText" dxfId="45" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="40" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="containsText" dxfId="44" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16146,7 +16122,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H20">
-    <cfRule type="containsText" dxfId="43" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16175,12 +16151,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G20">
-    <cfRule type="containsText" dxfId="42" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="41" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16197,7 +16173,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18">
-    <cfRule type="containsText" dxfId="40" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H18))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16214,7 +16190,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G31">
-    <cfRule type="containsText" dxfId="39" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16231,12 +16207,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="38" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G12">
-    <cfRule type="containsText" dxfId="37" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16253,7 +16229,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19">
-    <cfRule type="containsText" dxfId="36" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16270,7 +16246,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="containsText" dxfId="35" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16287,7 +16263,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25">
-    <cfRule type="containsText" dxfId="34" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16304,7 +16280,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="containsText" dxfId="33" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16321,7 +16297,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="containsText" dxfId="32" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16338,11 +16314,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32">
-    <cfRule type="containsText" dxfId="31" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H36 H34 H38">
+  <conditionalFormatting sqref="H34 H36 H38">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -16355,11 +16331,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34 H36 H38">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36 G34 G38">
+  <conditionalFormatting sqref="G34 G36 G38">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -16372,7 +16348,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34 G36 G38">
-    <cfRule type="containsText" dxfId="29" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16389,7 +16365,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16406,7 +16382,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H39))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16423,7 +16399,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G39">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G39))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17289,7 +17265,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F29">
-    <cfRule type="containsText" dxfId="27" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17318,7 +17294,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30">
-    <cfRule type="containsText" dxfId="26" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17335,41 +17311,41 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F28">
-    <cfRule type="containsText" dxfId="25" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F33 F31 F35">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F31 F33 F35">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F31 F33 F35">
-    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F34 F32">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F32 F34">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F32 F34">
-    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17386,7 +17362,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18268,7 +18244,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30">
-    <cfRule type="containsText" dxfId="22" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18285,11 +18261,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F28">
-    <cfRule type="containsText" dxfId="21" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35 F33">
+  <conditionalFormatting sqref="F33 F35">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -18302,11 +18278,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33 F35">
-    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34 F32 F36">
+  <conditionalFormatting sqref="F32 F34 F36">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -18319,7 +18295,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32 F34 F36">
-    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18336,7 +18312,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29">
-    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18353,7 +18329,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Collections/Ukraine/#Ukraine#Regular#[1992-present]#circulation_quality.xlsx
+++ b/Collections/Ukraine/#Ukraine#Regular#[1992-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Ukraine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD04F03-D1CC-479C-B536-6EBAA4FD7557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD39695-2CC9-49DA-ADC0-47C32E43D88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1копійка" sheetId="4" r:id="rId1"/>
@@ -4990,7 +4990,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21 H23">
+  <conditionalFormatting sqref="H23 H21">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6203,7 +6203,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32 F34 F36">
+  <conditionalFormatting sqref="F34 F32 F36">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7409,7 +7409,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21 H23">
+  <conditionalFormatting sqref="H23 H21">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8876,7 +8876,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21 H23 H25">
+  <conditionalFormatting sqref="H23 H21 H25">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10319,7 +10319,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22 H24 H26 H28 H34">
+  <conditionalFormatting sqref="H24 H22 H26 H28 H34">
     <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>0</v>
@@ -11967,7 +11967,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J23 J25 J27 J18:J21">
+  <conditionalFormatting sqref="J25 J23 J27 J18:J21">
     <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -12015,7 +12015,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J22 J24 J26">
+  <conditionalFormatting sqref="J24 J22 J26">
     <cfRule type="colorScale" priority="110">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13896,7 +13896,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22 H28">
+  <conditionalFormatting sqref="H28 H22">
     <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -15825,7 +15825,7 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H22 H27 H13:H17 H33 H35 H37">
+  <conditionalFormatting sqref="H27 H22 H13:H17 H33 H35 H37">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -15885,7 +15885,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21 H23 H26 H28 H30">
+  <conditionalFormatting sqref="H23 H21 H26 H28 H30">
     <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -16318,7 +16318,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34 H36 H38">
+  <conditionalFormatting sqref="H36 H34 H38">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -16335,7 +16335,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34 G36 G38">
+  <conditionalFormatting sqref="G36 G34 G38">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17315,7 +17315,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33 F31 F35">
+  <conditionalFormatting sqref="F31 F33 F35">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17332,7 +17332,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34 F32">
+  <conditionalFormatting sqref="F32 F34">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -18265,7 +18265,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33 F35">
+  <conditionalFormatting sqref="F35 F33">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -18282,7 +18282,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32 F34 F36">
+  <conditionalFormatting sqref="F34 F32 F36">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>

--- a/Collections/Ukraine/#Ukraine#Regular#[1992-present]#circulation_quality.xlsx
+++ b/Collections/Ukraine/#Ukraine#Regular#[1992-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Ukraine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD39695-2CC9-49DA-ADC0-47C32E43D88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280089EC-7B6F-4132-92C1-0645A62C0EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1копійка" sheetId="4" r:id="rId1"/>
@@ -779,7 +779,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="141">
   <si>
     <t>-</t>
   </si>
@@ -1341,7 +1341,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1471,13 +1471,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1571,6 +1586,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1602,7 +1626,7 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="248">
+  <dxfs count="263">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
@@ -1611,6 +1635,126 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -3910,25 +4054,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="30"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37" t="s">
+      <c r="D1" s="39"/>
+      <c r="E1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="39" t="s">
+      <c r="F1" s="41"/>
+      <c r="G1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="40"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
         <v>35</v>
       </c>
@@ -4242,7 +4386,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <v>2002</v>
       </c>
@@ -4262,7 +4406,7 @@
       <c r="G13" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="34">
         <v>0</v>
       </c>
       <c r="I13" s="12" t="str">
@@ -4290,8 +4434,8 @@
       <c r="G14" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H14" s="8">
-        <v>0</v>
+      <c r="H14" s="33">
+        <v>1</v>
       </c>
       <c r="I14" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4375,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4403,14 +4547,14 @@
         <v>0</v>
       </c>
       <c r="H18" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
         <v>2008</v>
       </c>
@@ -4430,7 +4574,7 @@
       <c r="G19" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="34">
         <v>1</v>
       </c>
       <c r="I19" s="12" t="str">
@@ -4459,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4487,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4964,12 +5108,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:G27 H24:H27 G29:H29">
-    <cfRule type="containsText" dxfId="247" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="262" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="246" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="261" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4986,7 +5130,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H10">
-    <cfRule type="containsText" dxfId="245" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="260" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5003,7 +5147,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21 H23">
-    <cfRule type="containsText" dxfId="244" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="259" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5019,8 +5163,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11:H20 H22">
-    <cfRule type="containsText" dxfId="243" priority="53" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H22 H11:H20">
+    <cfRule type="containsText" dxfId="258" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5037,7 +5181,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="242" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="257" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5054,7 +5198,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="241" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="256" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5071,7 +5215,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32:G33">
-    <cfRule type="containsText" dxfId="240" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="255" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5088,7 +5232,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G30:G31">
-    <cfRule type="containsText" dxfId="239" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="254" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5105,7 +5249,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="238" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="253" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5122,7 +5266,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="237" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="252" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5139,7 +5283,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30:H31">
-    <cfRule type="containsText" dxfId="236" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="251" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5156,7 +5300,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:H33">
-    <cfRule type="containsText" dxfId="235" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="250" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5173,7 +5317,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34:G36">
-    <cfRule type="containsText" dxfId="234" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="249" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5190,7 +5334,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:H36">
-    <cfRule type="containsText" dxfId="233" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="248" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5219,7 +5363,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="232" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="247" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5236,7 +5380,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="231" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="246" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5253,7 +5397,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="230" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="245" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5270,12 +5414,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="229" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="244" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="228" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="243" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5292,7 +5436,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="227" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="242" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5309,7 +5453,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="226" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="241" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5333,14 +5477,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="30"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
+      <c r="D1" s="39"/>
       <c r="E1" s="25" t="s">
         <v>3</v>
       </c>
@@ -5351,7 +5495,7 @@
       <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
         <v>35</v>
       </c>
@@ -6057,7 +6201,7 @@
         <v>67</v>
       </c>
       <c r="F31" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="19" t="str">
         <f t="shared" si="0"/>
@@ -6398,25 +6542,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="30"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37" t="s">
+      <c r="D1" s="39"/>
+      <c r="E1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="39" t="s">
+      <c r="F1" s="41"/>
+      <c r="G1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="40"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
         <v>35</v>
       </c>
@@ -6480,7 +6624,7 @@
       <c r="F4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="35">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="s">
@@ -6720,7 +6864,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <v>2002</v>
       </c>
@@ -6738,7 +6882,7 @@
       <c r="G13" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="34">
         <v>0</v>
       </c>
       <c r="I13" s="12" t="str">
@@ -6843,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6902,7 +7046,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="5">
         <v>2009</v>
       </c>
@@ -6920,8 +7064,8 @@
       <c r="G20" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H20" s="8">
-        <v>0</v>
+      <c r="H20" s="34">
+        <v>1</v>
       </c>
       <c r="I20" s="12" t="str">
         <f t="shared" si="0"/>
@@ -6947,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7385,8 +7529,8 @@
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="H12:H13 H22 H15:H20">
-    <cfRule type="colorScale" priority="58">
+  <conditionalFormatting sqref="H22 H12 H15:H19">
+    <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -7398,6 +7542,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:H10">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23 H21">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7409,30 +7565,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23 H21">
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H13 H22 H15:H20">
-    <cfRule type="containsText" dxfId="225" priority="57" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H12 H22 H15:H19">
+    <cfRule type="containsText" dxfId="240" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21 H23">
-    <cfRule type="containsText" dxfId="224" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="239" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:G27 H24:H27 G29:H29">
-    <cfRule type="colorScale" priority="62">
+    <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -7444,6 +7588,84 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:G27 H24:H27 G29:H29">
+    <cfRule type="containsText" dxfId="238" priority="65" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H10">
+    <cfRule type="containsText" dxfId="237" priority="63" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="containsText" dxfId="236" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="235" priority="51" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="containsText" dxfId="234" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="233" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7455,73 +7677,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G27 H24:H27 G29:H29">
-    <cfRule type="containsText" dxfId="223" priority="61" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H10">
-    <cfRule type="containsText" dxfId="222" priority="59" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="221" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="220" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="219" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="218" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="232" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7533,12 +7694,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="217" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="231" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="containsText" dxfId="230" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7550,46 +7728,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="216" priority="27" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G6">
+    <cfRule type="containsText" dxfId="229" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="containsText" dxfId="228" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="215" priority="25" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G4">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="containsText" dxfId="227" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="214" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
+  <conditionalFormatting sqref="G30:G31">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7601,179 +7779,179 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="213" priority="21" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G30:G31">
+    <cfRule type="containsText" dxfId="226" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30:H31">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30:H31">
+    <cfRule type="containsText" dxfId="225" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G32:G33">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G32:G33">
+    <cfRule type="containsText" dxfId="224" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32:H33">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32:H33">
+    <cfRule type="containsText" dxfId="223" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34:G36">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34:G36">
+    <cfRule type="containsText" dxfId="222" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34:H36">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34:H36">
+    <cfRule type="containsText" dxfId="221" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="containsText" dxfId="220" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="containsText" dxfId="219" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="containsText" dxfId="218" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="217" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="212" priority="19" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H20">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="216" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G31">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G31">
-    <cfRule type="containsText" dxfId="211" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30:H31">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30:H31">
-    <cfRule type="containsText" dxfId="210" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G32:G33">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G32:G33">
-    <cfRule type="containsText" dxfId="209" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32:H33">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32:H33">
-    <cfRule type="containsText" dxfId="208" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G36">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G36">
-    <cfRule type="containsText" dxfId="207" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H36">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H36">
-    <cfRule type="containsText" dxfId="206" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G28">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="205" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="204" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="203" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7796,25 +7974,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="30"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37" t="s">
+      <c r="D1" s="39"/>
+      <c r="E1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="39" t="s">
+      <c r="F1" s="41"/>
+      <c r="G1" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="40"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
         <v>35</v>
       </c>
@@ -8188,7 +8366,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>2004</v>
       </c>
@@ -8208,7 +8386,7 @@
       <c r="G15" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="34">
         <v>0</v>
       </c>
       <c r="I15" s="12" t="str">
@@ -8237,7 +8415,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="12" t="str">
         <f t="shared" si="0"/>
@@ -8328,7 +8506,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="5">
         <v>2009</v>
       </c>
@@ -8348,8 +8526,8 @@
       <c r="G20" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H20" s="8">
-        <v>0</v>
+      <c r="H20" s="34">
+        <v>1</v>
       </c>
       <c r="I20" s="12" t="str">
         <f t="shared" si="0"/>
@@ -8377,7 +8555,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="12" t="str">
         <f t="shared" si="0"/>
@@ -8468,7 +8646,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="5">
         <v>2014</v>
       </c>
@@ -8488,7 +8666,7 @@
       <c r="G25" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="34">
         <v>0</v>
       </c>
       <c r="I25" s="12" t="str">
@@ -8828,7 +9006,87 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H14:H20 H22 H24 H26">
+  <conditionalFormatting sqref="H22 H14 H24 H26 H16:H19">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:G12 G14:G27 G29">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H10">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23 H21">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14 H22 H24 H26 H16:H19">
+    <cfRule type="containsText" dxfId="215" priority="59" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21 H23">
+    <cfRule type="containsText" dxfId="214" priority="57" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:G12 G14:G27 G29">
+    <cfRule type="containsText" dxfId="213" priority="67" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="212" priority="65" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8840,451 +9098,422 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G12 G14:G27 G29">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="containsText" dxfId="211" priority="55" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:H10">
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23 H21 H25">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14:H20 H22 H24 H26">
-    <cfRule type="containsText" dxfId="202" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="210" priority="61" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="containsText" dxfId="209" priority="53" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="208" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="207" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="containsText" dxfId="206" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="containsText" dxfId="205" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="containsText" dxfId="204" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="containsText" dxfId="203" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21 H23 H25">
-    <cfRule type="containsText" dxfId="201" priority="51" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="202" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30:G31">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30:G31">
+    <cfRule type="containsText" dxfId="201" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30:H31">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30:H31">
+    <cfRule type="containsText" dxfId="200" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G32:G33">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G32:G33">
+    <cfRule type="containsText" dxfId="199" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32:H33">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32:H33">
+    <cfRule type="containsText" dxfId="198" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34:G36">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34:G36">
+    <cfRule type="containsText" dxfId="197" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34:H36">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34:H36">
+    <cfRule type="containsText" dxfId="196" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="195" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="containsText" dxfId="194" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="193" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="containsText" dxfId="192" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="containsText" dxfId="191" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="containsText" dxfId="190" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="189" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="containsText" dxfId="188" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G12 G14:G27 G29">
-    <cfRule type="containsText" dxfId="200" priority="61" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="199" priority="59" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H20">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="187" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="198" priority="49" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H25">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25">
+    <cfRule type="containsText" dxfId="186" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H10">
-    <cfRule type="containsText" dxfId="197" priority="55" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="196" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="195" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="194" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="193" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="192" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="191" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="190" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="189" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G31">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G31">
-    <cfRule type="containsText" dxfId="188" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30:H31">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30:H31">
-    <cfRule type="containsText" dxfId="187" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G32:G33">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G32:G33">
-    <cfRule type="containsText" dxfId="186" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32:H33">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32:H33">
-    <cfRule type="containsText" dxfId="185" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G36">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G36">
-    <cfRule type="containsText" dxfId="184" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H36">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H36">
-    <cfRule type="containsText" dxfId="183" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="182" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="containsText" dxfId="181" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="180" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="179" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G28">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="178" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="177" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="176" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9307,25 +9536,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="30"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37" t="s">
+      <c r="D1" s="39"/>
+      <c r="E1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="39" t="s">
+      <c r="F1" s="41"/>
+      <c r="G1" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="40"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
         <v>35</v>
       </c>
@@ -9711,7 +9940,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="5">
         <v>2004</v>
       </c>
@@ -9729,7 +9958,7 @@
       <c r="G16" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="34">
         <v>1</v>
       </c>
       <c r="I16" s="12" t="str">
@@ -9867,7 +10096,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
         <v>2010</v>
       </c>
@@ -9885,7 +10114,7 @@
       <c r="G22" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="34">
         <v>1</v>
       </c>
       <c r="I22" s="12" t="str">
@@ -10023,7 +10252,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="5">
         <v>2016</v>
       </c>
@@ -10041,7 +10270,7 @@
       <c r="G28" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="34">
         <v>0</v>
       </c>
       <c r="I28" s="12" t="str">
@@ -10307,20 +10536,20 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H14:H21 H23 H25 H27 H31 G4:H4">
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24 H22 H26 H28 H34">
-    <cfRule type="colorScale" priority="66">
+  <conditionalFormatting sqref="H14:H15 H23 H25 H27 H31 G4:H4 H17:H21">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26 H24 H34">
+    <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -10332,29 +10561,29 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H11">
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14:H21 H23 H25 H27 H31">
-    <cfRule type="containsText" dxfId="175" priority="67" operator="containsText" text="*-">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14:H15 H23 H25 H27 H31 H17:H21">
+    <cfRule type="containsText" dxfId="185" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22 H24 H26 H28 H34">
-    <cfRule type="containsText" dxfId="174" priority="65" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H24 H26 H34">
+    <cfRule type="containsText" dxfId="184" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G12 G14:G28 G31:G34">
-    <cfRule type="colorScale" priority="72">
+    <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -10366,7 +10595,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7">
-    <cfRule type="colorScale" priority="46">
+    <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -10378,7 +10607,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="colorScale" priority="50">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -10390,7 +10619,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="colorScale" priority="58">
+    <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -10402,31 +10631,60 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G12 G14:G28 G31:G34 H4">
-    <cfRule type="containsText" dxfId="173" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="183" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H11">
-    <cfRule type="containsText" dxfId="172" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="182" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="171" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="181" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="170" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="180" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="169" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="179" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="178" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10438,12 +10696,39 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="168" priority="41" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="containsText" dxfId="177" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="containsText" dxfId="176" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6">
+    <cfRule type="containsText" dxfId="175" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="containsText" dxfId="174" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10455,19 +10740,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
+  <conditionalFormatting sqref="G8">
+    <cfRule type="containsText" dxfId="173" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -10479,221 +10757,223 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="167" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="166" priority="39" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G13">
+    <cfRule type="containsText" dxfId="172" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32:H33">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32:H33">
+    <cfRule type="containsText" dxfId="171" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35:G37">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35:G37">
+    <cfRule type="containsText" dxfId="170" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35:H37">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35:H37">
+    <cfRule type="containsText" dxfId="169" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30">
+    <cfRule type="containsText" dxfId="168" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
+    <cfRule type="containsText" dxfId="167" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="containsText" dxfId="166" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="165" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:H3">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="164" priority="12" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="163" priority="10" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="165" priority="37" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="162" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="161" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="containsText" dxfId="160" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="164" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="163" priority="31" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H22">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="containsText" dxfId="159" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="containsText" dxfId="162" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32:H33">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32:H33">
-    <cfRule type="containsText" dxfId="161" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G35:G37">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G35:G37">
-    <cfRule type="containsText" dxfId="160" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35:H37">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35:H37">
-    <cfRule type="containsText" dxfId="159" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G30">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G30">
-    <cfRule type="containsText" dxfId="158" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="containsText" dxfId="157" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="containsText" dxfId="156" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="155" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:H3">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="154" priority="6" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="153" priority="4" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H28">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="containsText" dxfId="158" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="152" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="151" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10717,27 +10997,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="30"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37" t="s">
+      <c r="D1" s="39"/>
+      <c r="E1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="41"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="39" t="s">
+      <c r="F1" s="44"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
         <v>35</v>
       </c>
@@ -10919,7 +11199,7 @@
       <c r="H7" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="8" t="s">
         <v>0</v>
       </c>
       <c r="J7" s="8" t="s">
@@ -10930,7 +11210,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <v>1996</v>
       </c>
@@ -10951,7 +11231,7 @@
       <c r="H8" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="34">
         <v>0</v>
       </c>
       <c r="J8" s="8" t="s">
@@ -11403,7 +11683,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
         <v>2010</v>
       </c>
@@ -11427,7 +11707,7 @@
       <c r="I22" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="34">
         <v>1</v>
       </c>
       <c r="K22" s="15" t="str">
@@ -11956,18 +12236,129 @@
     <mergeCell ref="H1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="J6">
-    <cfRule type="colorScale" priority="94">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J25 J23 J27 J18:J21">
+    <cfRule type="colorScale" priority="100">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23 J25 J27 J18:J21">
+    <cfRule type="colorScale" priority="118">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10:H11 H14:H16 H30 H18:H28">
+    <cfRule type="colorScale" priority="126">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="colorScale" priority="110">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8:J11">
+    <cfRule type="colorScale" priority="120">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J26 J24">
+    <cfRule type="colorScale" priority="116">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23 J25 J27 J18:J21">
+    <cfRule type="containsText" dxfId="157" priority="117" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J24 J26">
+    <cfRule type="containsText" dxfId="156" priority="115" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10:H11 H14:H16 H30 H18:H28">
+    <cfRule type="containsText" dxfId="155" priority="125" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9:I11 I14:I16 I30 I18:I28">
+    <cfRule type="colorScale" priority="122">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5">
+    <cfRule type="colorScale" priority="108">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H9">
     <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11979,745 +12370,651 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:H11 H14:H16 H30 H18:H28">
-    <cfRule type="colorScale" priority="120">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
+  <conditionalFormatting sqref="J3">
+    <cfRule type="colorScale" priority="104">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9:I11 I14:I16 I30 I18:I28">
+    <cfRule type="containsText" dxfId="154" priority="121" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8:J11">
+    <cfRule type="containsText" dxfId="153" priority="119" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I31:I32">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H9">
+    <cfRule type="containsText" dxfId="152" priority="111" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="colorScale" priority="104">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J8:J11">
-    <cfRule type="colorScale" priority="114">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J24 J22 J26">
-    <cfRule type="colorScale" priority="110">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J23 J25 J27 J18:J21">
-    <cfRule type="containsText" dxfId="150" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="151" priority="109" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5">
+    <cfRule type="containsText" dxfId="150" priority="107" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="149" priority="91" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3">
+    <cfRule type="containsText" dxfId="148" priority="103" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6">
+    <cfRule type="containsText" dxfId="147" priority="99" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="colorScale" priority="96">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="containsText" dxfId="146" priority="95" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J12">
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12">
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12">
+    <cfRule type="containsText" dxfId="145" priority="89" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J12">
+    <cfRule type="containsText" dxfId="144" priority="87" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6">
+    <cfRule type="containsText" dxfId="143" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J22 J24 J26">
-    <cfRule type="containsText" dxfId="149" priority="109" operator="containsText" text="*-">
+  <conditionalFormatting sqref="J14">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14">
+    <cfRule type="containsText" dxfId="142" priority="73" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="141" priority="71" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
+    <cfRule type="containsText" dxfId="140" priority="69" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J35:J37">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J35:J37">
+    <cfRule type="containsText" dxfId="139" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I35:I37">
+    <cfRule type="containsText" dxfId="138" priority="53" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J29">
+    <cfRule type="containsText" dxfId="137" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31:H32">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31:H32">
+    <cfRule type="containsText" dxfId="136" priority="63" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I31:I32">
+    <cfRule type="containsText" dxfId="135" priority="61" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33:H34">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33:H34">
+    <cfRule type="containsText" dxfId="134" priority="59" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I33:I34">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I33:I34">
+    <cfRule type="containsText" dxfId="133" priority="57" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35:H37">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35:H37">
+    <cfRule type="containsText" dxfId="132" priority="55" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I35:I37">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J31:J32">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J31:J32">
+    <cfRule type="containsText" dxfId="131" priority="51" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J33:J34">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J33:J34">
+    <cfRule type="containsText" dxfId="130" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="129" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29">
+    <cfRule type="containsText" dxfId="128" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J29">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J4">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J4">
+    <cfRule type="containsText" dxfId="127" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="containsText" dxfId="126" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:H11 H14:H16 H30 H18:H28">
-    <cfRule type="containsText" dxfId="148" priority="119" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I9:I11 I14:I16 I30 I18:I28">
-    <cfRule type="colorScale" priority="116">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="colorScale" priority="86">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5">
-    <cfRule type="colorScale" priority="102">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H9">
-    <cfRule type="colorScale" priority="106">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3">
-    <cfRule type="colorScale" priority="98">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I9:I11 I14:I16 I30 I18:I28">
-    <cfRule type="containsText" dxfId="147" priority="115" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J8:J11">
-    <cfRule type="containsText" dxfId="146" priority="113" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I31:I32">
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H9">
-    <cfRule type="containsText" dxfId="145" priority="105" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5">
-    <cfRule type="containsText" dxfId="144" priority="103" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="125" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="containsText" dxfId="124" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="123" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J16">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="containsText" dxfId="122" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I17">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I17">
+    <cfRule type="containsText" dxfId="121" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J17">
+    <cfRule type="containsText" dxfId="120" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J16">
+    <cfRule type="containsText" dxfId="119" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J15">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J15">
+    <cfRule type="containsText" dxfId="118" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J13">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J13">
+    <cfRule type="containsText" dxfId="117" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J30">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J30">
+    <cfRule type="containsText" dxfId="116" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J28">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J28">
+    <cfRule type="containsText" dxfId="115" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="containsText" dxfId="114" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5">
-    <cfRule type="containsText" dxfId="143" priority="101" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="142" priority="85" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3">
-    <cfRule type="containsText" dxfId="141" priority="97" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6">
-    <cfRule type="containsText" dxfId="140" priority="93" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="colorScale" priority="90">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="containsText" dxfId="139" priority="89" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="138" priority="73" operator="containsText" text="*-">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8">
+    <cfRule type="containsText" dxfId="113" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J12">
-    <cfRule type="colorScale" priority="82">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I12">
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="137" priority="83" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="136" priority="81" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="colorScale" priority="66">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6">
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6">
-    <cfRule type="containsText" dxfId="135" priority="77" operator="containsText" text="*-">
+  <conditionalFormatting sqref="J22">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22">
+    <cfRule type="containsText" dxfId="112" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="134" priority="75" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J14">
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="133" priority="67" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="132" priority="65" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="131" priority="63" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J35:J37">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J35:J37">
-    <cfRule type="containsText" dxfId="130" priority="41" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I35:I37">
-    <cfRule type="containsText" dxfId="129" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J29">
-    <cfRule type="containsText" dxfId="128" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31:H32">
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31:H32">
-    <cfRule type="containsText" dxfId="127" priority="57" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I31:I32">
-    <cfRule type="containsText" dxfId="126" priority="55" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H33:H34">
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H33:H34">
-    <cfRule type="containsText" dxfId="125" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I33:I34">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I33:I34">
-    <cfRule type="containsText" dxfId="124" priority="51" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35:H37">
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35:H37">
-    <cfRule type="containsText" dxfId="123" priority="49" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I35:I37">
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J31:J32">
-    <cfRule type="colorScale" priority="46">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J31:J32">
-    <cfRule type="containsText" dxfId="122" priority="45" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J33:J34">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J33:J34">
-    <cfRule type="containsText" dxfId="121" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="120" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I29">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I29">
-    <cfRule type="containsText" dxfId="119" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J29">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J4">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J4">
-    <cfRule type="containsText" dxfId="118" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="117" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="116" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="115" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="114" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J16">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17">
-    <cfRule type="containsText" dxfId="113" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I17">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I17">
-    <cfRule type="containsText" dxfId="112" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J17">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J17">
-    <cfRule type="containsText" dxfId="111" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J16">
-    <cfRule type="containsText" dxfId="110" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J15">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="109" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J13">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="108" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J30">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J30">
-    <cfRule type="containsText" dxfId="107" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J28">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J28">
-    <cfRule type="containsText" dxfId="106" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J28))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12740,25 +13037,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="30"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37" t="s">
+      <c r="D1" s="39"/>
+      <c r="E1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="39" t="s">
+      <c r="F1" s="41"/>
+      <c r="G1" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="40"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
         <v>35</v>
       </c>
@@ -12878,7 +13175,7 @@
       <c r="F6" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="35">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -13202,7 +13499,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="5">
         <v>2006</v>
       </c>
@@ -13222,7 +13519,7 @@
       <c r="G18" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="34">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="str">
@@ -13426,7 +13723,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
         <v>2013</v>
       </c>
@@ -13446,7 +13743,7 @@
       <c r="G26" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="34">
         <v>0</v>
       </c>
       <c r="I26" s="12" t="str">
@@ -13860,8 +14157,8 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H18:H21 G28 G30">
-    <cfRule type="colorScale" priority="166">
+  <conditionalFormatting sqref="H19:H21 G28 G30">
+    <cfRule type="colorScale" priority="170">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -13873,6 +14170,76 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
+    <cfRule type="colorScale" priority="164">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8:H11">
+    <cfRule type="colorScale" priority="172">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28 H22">
+    <cfRule type="colorScale" priority="168">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19:H21">
+    <cfRule type="containsText" dxfId="111" priority="169" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22 H28">
+    <cfRule type="containsText" dxfId="110" priority="167" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9:G11 G14:G24 G32:G33">
+    <cfRule type="colorScale" priority="174">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="colorScale" priority="162">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
     <cfRule type="colorScale" priority="160">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13884,216 +14251,270 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G9:G11 G14:G24 G32:G33 G28 G30">
+    <cfRule type="containsText" dxfId="109" priority="173" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H8:H11">
-    <cfRule type="colorScale" priority="168">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28 H22">
-    <cfRule type="colorScale" priority="164">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18:H21">
-    <cfRule type="containsText" dxfId="105" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="108" priority="171" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="colorScale" priority="158">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="containsText" dxfId="107" priority="163" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="containsText" dxfId="106" priority="161" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="105" priority="159" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="containsText" dxfId="104" priority="157" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
+    <cfRule type="colorScale" priority="156">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
+    <cfRule type="containsText" dxfId="103" priority="155" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="colorScale" priority="150">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="colorScale" priority="152">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="containsText" dxfId="102" priority="151" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="101" priority="149" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="colorScale" priority="144">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="containsText" dxfId="100" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22 H28">
-    <cfRule type="containsText" dxfId="104" priority="163" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H14">
+    <cfRule type="colorScale" priority="140">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="colorScale" priority="136">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="containsText" dxfId="99" priority="139" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="containsText" dxfId="98" priority="135" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="colorScale" priority="118">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="containsText" dxfId="97" priority="117" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9:G11 G14:G24 G32:G33">
-    <cfRule type="colorScale" priority="170">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="colorScale" priority="158">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="colorScale" priority="156">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G9:G11 G14:G24 G32:G33 G28 G30">
-    <cfRule type="containsText" dxfId="103" priority="169" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H11">
-    <cfRule type="containsText" dxfId="102" priority="167" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="colorScale" priority="154">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="101" priority="159" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="containsText" dxfId="100" priority="157" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="99" priority="155" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="98" priority="153" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
-    <cfRule type="colorScale" priority="152">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="97" priority="151" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="colorScale" priority="146">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="colorScale" priority="148">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="containsText" dxfId="96" priority="147" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="95" priority="145" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
-    <cfRule type="colorScale" priority="140">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="94" priority="139" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G4">
+    <cfRule type="colorScale" priority="128">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="containsText" dxfId="96" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="colorScale" priority="136">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="colorScale" priority="132">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="93" priority="135" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
+  <conditionalFormatting sqref="H31">
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
+    <cfRule type="containsText" dxfId="95" priority="87" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="colorScale" priority="112">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="94" priority="111" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G31">
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="colorScale" priority="98">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="containsText" dxfId="93" priority="97" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G31">
+    <cfRule type="containsText" dxfId="92" priority="89" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G31))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
+    <cfRule type="containsText" dxfId="91" priority="83" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -14105,290 +14526,506 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="containsText" dxfId="92" priority="131" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="colorScale" priority="114">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="91" priority="113" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G34">
+    <cfRule type="containsText" dxfId="90" priority="79" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="containsText" dxfId="89" priority="63" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="88" priority="69" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="87" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="colorScale" priority="124">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="90" priority="123" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G8">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="containsText" dxfId="86" priority="61" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="containsText" dxfId="85" priority="59" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="containsText" dxfId="84" priority="57" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23:H24">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23:H24">
+    <cfRule type="containsText" dxfId="83" priority="55" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="containsText" dxfId="82" priority="51" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
+    <cfRule type="containsText" dxfId="81" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="containsText" dxfId="80" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25">
+    <cfRule type="containsText" dxfId="79" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25">
+    <cfRule type="containsText" dxfId="78" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H38">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="containsText" dxfId="77" priority="36" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="76" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
+    <cfRule type="containsText" dxfId="75" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34">
+    <cfRule type="containsText" dxfId="74" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35">
+    <cfRule type="containsText" dxfId="73" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G36">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G36">
+    <cfRule type="containsText" dxfId="72" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G36))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35">
+    <cfRule type="containsText" dxfId="71" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H36">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H36">
+    <cfRule type="containsText" dxfId="70" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H36))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37">
+    <cfRule type="containsText" dxfId="69" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G37))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37">
+    <cfRule type="containsText" dxfId="68" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
-    <cfRule type="containsText" dxfId="89" priority="83" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G39">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G39">
+    <cfRule type="containsText" dxfId="67" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G39))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H39">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H39">
+    <cfRule type="containsText" dxfId="66" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="colorScale" priority="108">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="88" priority="107" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G31">
-    <cfRule type="colorScale" priority="86">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
-    <cfRule type="colorScale" priority="94">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
-    <cfRule type="containsText" dxfId="87" priority="93" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G31">
-    <cfRule type="containsText" dxfId="86" priority="85" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32">
-    <cfRule type="containsText" dxfId="85" priority="79" operator="containsText" text="*-">
+  <conditionalFormatting sqref="H38">
+    <cfRule type="containsText" dxfId="65" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34">
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G34">
-    <cfRule type="containsText" dxfId="84" priority="75" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="83" priority="59" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="66">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="82" priority="65" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="81" priority="61" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G38">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G38">
+    <cfRule type="containsText" dxfId="64" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G38))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H40">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H40">
+    <cfRule type="containsText" dxfId="63" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
-    <cfRule type="containsText" dxfId="80" priority="57" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="containsText" dxfId="79" priority="55" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17">
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17">
-    <cfRule type="containsText" dxfId="78" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23:H24">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23:H24">
-    <cfRule type="containsText" dxfId="77" priority="51" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="76" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="colorScale" priority="46">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="containsText" dxfId="75" priority="45" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
+  <conditionalFormatting sqref="G40">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G40">
+    <cfRule type="containsText" dxfId="62" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G40))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="containsText" dxfId="61" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="colorScale" priority="42">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -14400,331 +15037,8 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="74" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="containsText" dxfId="73" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
-    <cfRule type="containsText" dxfId="72" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
-    <cfRule type="containsText" dxfId="71" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H38">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="containsText" dxfId="70" priority="32" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="69" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H33">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H33">
-    <cfRule type="containsText" dxfId="68" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H34">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H34">
-    <cfRule type="containsText" dxfId="67" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G35">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G35">
-    <cfRule type="containsText" dxfId="66" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G36">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G36">
-    <cfRule type="containsText" dxfId="65" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G36))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35">
-    <cfRule type="containsText" dxfId="64" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H36">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H36">
-    <cfRule type="containsText" dxfId="63" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H36))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G37">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G37">
-    <cfRule type="containsText" dxfId="62" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G37))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H37">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H37">
-    <cfRule type="containsText" dxfId="61" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G39">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G39">
-    <cfRule type="containsText" dxfId="60" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G39))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H39">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H39">
-    <cfRule type="containsText" dxfId="59" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H38">
-    <cfRule type="containsText" dxfId="58" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G38">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G38">
-    <cfRule type="containsText" dxfId="57" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G38))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H40">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H40">
-    <cfRule type="containsText" dxfId="56" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G40">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G40">
-    <cfRule type="containsText" dxfId="55" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G40))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14747,25 +15061,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="30"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37" t="s">
+      <c r="D1" s="39"/>
+      <c r="E1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="39" t="s">
+      <c r="F1" s="41"/>
+      <c r="G1" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="40"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
         <v>35</v>
       </c>
@@ -15125,7 +15439,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>2004</v>
       </c>
@@ -15145,7 +15459,7 @@
       <c r="G15" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="34">
         <v>1</v>
       </c>
       <c r="I15" s="12" t="str">
@@ -15318,7 +15632,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="12" t="str">
         <f t="shared" si="0"/>
@@ -15353,7 +15667,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="5">
         <v>2012</v>
       </c>
@@ -15373,7 +15687,7 @@
       <c r="G23" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="34">
         <v>0</v>
       </c>
       <c r="I23" s="12" t="str">
@@ -15624,7 +15938,7 @@
       </c>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="5">
         <v>2019</v>
       </c>
@@ -15644,7 +15958,7 @@
       <c r="G33" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="34">
         <v>0</v>
       </c>
       <c r="I33" s="12" t="str">
@@ -15764,7 +16078,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="24">
         <v>2024</v>
       </c>
@@ -15784,7 +16098,7 @@
       <c r="G38" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="34">
         <v>0</v>
       </c>
       <c r="I38" s="12" t="str">
@@ -15825,7 +16139,106 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H27 H22 H13:H17 H33 H35 H37">
+  <conditionalFormatting sqref="H22 H27 H13:H14 H35 H37 H16:H17">
+    <cfRule type="colorScale" priority="106">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="96">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G5">
+    <cfRule type="colorScale" priority="100">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H10">
+    <cfRule type="colorScale" priority="108">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26 H21 H28 H30">
+    <cfRule type="colorScale" priority="104">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22 H27 H13:H14 H35 H37 H16:H17">
+    <cfRule type="containsText" dxfId="59" priority="105" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21 H26 H28 H30">
+    <cfRule type="containsText" dxfId="58" priority="103" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="57" priority="95" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:G10 G14:G17 G30 G21:G24 G19 G26:G28 G33 G35 G37">
+    <cfRule type="colorScale" priority="110">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H5">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -15837,7 +16250,78 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
+  <conditionalFormatting sqref="G7">
+    <cfRule type="containsText" dxfId="56" priority="81" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:G10 G14:G17 G30 G21:G24 G19 G26:G28 G33 G35 G37">
+    <cfRule type="containsText" dxfId="55" priority="109" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H10">
+    <cfRule type="containsText" dxfId="54" priority="107" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G5">
+    <cfRule type="containsText" dxfId="53" priority="99" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H5">
+    <cfRule type="containsText" dxfId="52" priority="97" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="containsText" dxfId="51" priority="59" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="containsText" dxfId="50" priority="91" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
     <cfRule type="colorScale" priority="88">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -15849,335 +16333,323 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G5">
-    <cfRule type="colorScale" priority="92">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H10">
-    <cfRule type="colorScale" priority="100">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23 H21 H26 H28 H30">
-    <cfRule type="colorScale" priority="96">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22 H27 H13:H17 H33 H35 H37">
-    <cfRule type="containsText" dxfId="54" priority="97" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G11">
+    <cfRule type="containsText" dxfId="49" priority="87" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="48" priority="85" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="containsText" dxfId="47" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="containsText" dxfId="46" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="containsText" dxfId="45" priority="53" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
+    <cfRule type="containsText" dxfId="44" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="43" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="42" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="41" priority="51" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="containsText" dxfId="40" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G31">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G31">
+    <cfRule type="containsText" dxfId="39" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="38" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21 H23 H26 H28 H30">
-    <cfRule type="containsText" dxfId="53" priority="95" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G12">
+    <cfRule type="containsText" dxfId="37" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="36" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32">
+    <cfRule type="containsText" dxfId="35" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25">
+    <cfRule type="containsText" dxfId="34" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25">
+    <cfRule type="containsText" dxfId="33" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
+    <cfRule type="containsText" dxfId="32" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G32">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G32">
+    <cfRule type="containsText" dxfId="31" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H36 H34">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34 H36">
+    <cfRule type="containsText" dxfId="30" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="52" priority="87" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G10 G14:G17 G30 G21:G24 G19 G26:G28 G33 G35 G37">
-    <cfRule type="colorScale" priority="102">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H5">
-    <cfRule type="colorScale" priority="90">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="51" priority="73" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G10 G14:G17 G30 G21:G24 G19 G26:G28 G33 G35 G37">
-    <cfRule type="containsText" dxfId="50" priority="101" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H10">
-    <cfRule type="containsText" dxfId="49" priority="99" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G5">
-    <cfRule type="containsText" dxfId="48" priority="91" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H5">
-    <cfRule type="containsText" dxfId="47" priority="89" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="containsText" dxfId="46" priority="51" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="45" priority="83" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="44" priority="79" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="43" priority="77" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="42" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
-    <cfRule type="containsText" dxfId="41" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="colorScale" priority="46">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="containsText" dxfId="40" priority="45" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="containsText" dxfId="39" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
-    <cfRule type="containsText" dxfId="38" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G20">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G20">
-    <cfRule type="containsText" dxfId="37" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="36" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18">
-    <cfRule type="containsText" dxfId="35" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G31">
+  <conditionalFormatting sqref="G36 G34 G38">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -16189,51 +16661,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G31">
-    <cfRule type="containsText" dxfId="34" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="33" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="containsText" dxfId="32" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H19">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H19">
-    <cfRule type="containsText" dxfId="31" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32">
+  <conditionalFormatting sqref="G34 G36 G38">
+    <cfRule type="containsText" dxfId="29" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="28" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H39">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H39">
+    <cfRule type="containsText" dxfId="27" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H39))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G39">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -16245,80 +16712,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H32">
-    <cfRule type="containsText" dxfId="30" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
-    <cfRule type="containsText" dxfId="29" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
-    <cfRule type="containsText" dxfId="28" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
-    <cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G32">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G32">
-    <cfRule type="containsText" dxfId="26" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H36 H34 H38">
+  <conditionalFormatting sqref="G39">
+    <cfRule type="containsText" dxfId="26" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G39))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -16330,29 +16729,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34 H36 H38">
+  <conditionalFormatting sqref="H15">
     <cfRule type="containsText" dxfId="25" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36 G34 G38">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G34 G36 G38">
-    <cfRule type="containsText" dxfId="24" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="H23">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -16364,12 +16746,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="23" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H39">
+  <conditionalFormatting sqref="H23">
+    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
+    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H38">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -16381,26 +16780,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H39">
+  <conditionalFormatting sqref="H38">
     <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H39))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G39">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G39">
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G39))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16423,14 +16805,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="30"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
+      <c r="D1" s="39"/>
       <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
@@ -16441,7 +16823,7 @@
       <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
         <v>35</v>
       </c>
@@ -17166,7 +17548,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="24">
         <v>2022</v>
       </c>
@@ -17178,7 +17560,7 @@
       <c r="E33" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="34">
         <v>0</v>
       </c>
       <c r="G33" s="19" t="str">
@@ -17265,11 +17647,23 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F29">
-    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17281,7 +17675,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
+  <conditionalFormatting sqref="F30">
+    <cfRule type="containsText" dxfId="20" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F28">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17293,29 +17692,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F30">
-    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F3:F28">
+    <cfRule type="containsText" dxfId="19" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F35 F31">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31 F35">
+    <cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F28">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F28">
-    <cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F31 F33 F35">
+  <conditionalFormatting sqref="F32 F34">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17327,12 +17726,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31 F33 F35">
+  <conditionalFormatting sqref="F32 F34">
     <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32 F34">
+  <conditionalFormatting sqref="F36">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17344,26 +17743,26 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32 F34">
+  <conditionalFormatting sqref="F36">
     <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F36))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F36))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17386,14 +17785,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="30"/>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36"/>
+      <c r="D1" s="39"/>
       <c r="E1" s="25" t="s">
         <v>3</v>
       </c>
@@ -17404,7 +17803,7 @@
       <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="34"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="31" t="s">
         <v>35</v>
       </c>
